--- a/Sharedpointrequest/CurrentExcelItem.xlsx
+++ b/Sharedpointrequest/CurrentExcelItem.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA Folders\Migration\Fusion_ICRules\Sharedpointrequest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38992A11-8F73-45AE-9973-8FF5790F689C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC803D27-FA3C-48D4-87AF-E6432DFE7B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8FCA5C39-5E67-4CCE-A121-DDCB5A04A7C9}"/>
+    <workbookView xWindow="4245" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{BA92EEC4-E084-4429-A8B5-E13039E2C393}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,819 +39,825 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="271">
-  <si>
-    <t>1117 - LexisNexis Risk Solutions Inc.</t>
-  </si>
-  <si>
-    <t>1506 - LexisNexis Risk Solutions (Europe) Ltd</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="273">
+  <si>
+    <t>FROM_LEGAL_ENTITY_NAME</t>
+  </si>
+  <si>
+    <t>TO_LEGAL_ENTITY_NAME</t>
+  </si>
+  <si>
+    <t>FROM_LEDGER_NAME</t>
+  </si>
+  <si>
+    <t>TO_LEDGER_NAME</t>
+  </si>
+  <si>
+    <t>JE_SOURCE_NAME</t>
+  </si>
+  <si>
+    <t>JE_CATEGORY_NAME</t>
+  </si>
+  <si>
+    <t>TRX_TYPE_ID</t>
+  </si>
+  <si>
+    <t>START_DATE</t>
+  </si>
+  <si>
+    <t>END_DATE</t>
+  </si>
+  <si>
+    <t>Receivables Account</t>
+  </si>
+  <si>
+    <t>Payables Account</t>
+  </si>
+  <si>
+    <t>Source File</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>3406 - LexisNexis Business Information Solutions SA</t>
+  </si>
+  <si>
+    <t>3408 - LexisNexis SA</t>
+  </si>
+  <si>
+    <t>FR_EUR_CCR_PRIMARY</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>All Other</t>
+  </si>
+  <si>
+    <t>2020-01-01T00:00:00.000+00:00</t>
+  </si>
+  <si>
+    <t>31/8/2026</t>
+  </si>
+  <si>
+    <t>3406-999999-135101-XX0000-FR41218800-9999999-3408-0000-999999</t>
+  </si>
+  <si>
+    <t>3406-999999-204101-XX0000-FR40113100-9999999-3408-0000-999999</t>
+  </si>
+  <si>
+    <t>End Date file</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>3406-999999-135109-XX0000-FR41218800-9999999-3408-0000-999999</t>
+  </si>
+  <si>
+    <t>3406-999999-204109-XX0000-FR40113100-9999999-3408-0000-999999</t>
+  </si>
+  <si>
+    <t>New Rule file</t>
+  </si>
+  <si>
+    <t>Receivables/Payables Account combination cannot be used; it either does not exist, or using it here is not permitted.</t>
+  </si>
+  <si>
+    <t>3511 - LexisNexis GmbH</t>
+  </si>
+  <si>
+    <t>DE_EUR_CCR_PRIMARY</t>
+  </si>
+  <si>
+    <t>3406-999999-135101-XX0000-FR41218800-9999999-3511-0000-999999</t>
+  </si>
+  <si>
+    <t>3406-999999-204101-XX0000-FR40113100-9999999-3511-0000-999999</t>
+  </si>
+  <si>
+    <t>3406-999999-135109-XX0000-FR41218800-9999999-3511-0000-999999</t>
+  </si>
+  <si>
+    <t>3406-999999-204109-XX0000-FR40113100-9999999-3511-0000-999999</t>
+  </si>
+  <si>
+    <t>3110 - RELX Inc. (LEXNEX)</t>
   </si>
   <si>
     <t>US_USD_CCR_PRIMARY</t>
   </si>
   <si>
-    <t>IE_EUR_CCR_PRIMARY</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>All Other</t>
-  </si>
-  <si>
-    <t>2020-01-01T00:00:00.000+00:00</t>
-  </si>
-  <si>
-    <t>31/8/2026</t>
-  </si>
-  <si>
-    <t>1117-999999-135101-XX0000-XX99999999-9999999-1506-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-204101-XX0000-XX99999999-9999999-1506-0000-999999</t>
-  </si>
-  <si>
-    <t>End Date file</t>
-  </si>
-  <si>
-    <t>1117-999999-135109-XX0000-XX99999999-9999999-1506-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-204109-XX0000-XX99999999-9999999-1506-0000-999999</t>
-  </si>
-  <si>
-    <t>New Rule file</t>
-  </si>
-  <si>
-    <t>1701 - LNRS Data Services (Australia) Pty Ltd</t>
+    <t>3408-999999-135101-XX0000-FR41218800-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204101-XX0000-FR40113100-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-135109-XX0000-FR41218800-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204109-XX0000-FR40113100-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3204 - RELX (UK) Limited (LN)</t>
+  </si>
+  <si>
+    <t>UK_GBP_CCR_PRIMARY</t>
+  </si>
+  <si>
+    <t>3408-999999-135101-XX0000-FR41218800-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204101-XX0000-FR40113100-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-135109-XX0000-FR41218800-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204109-XX0000-FR40113100-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3302 - LexisNexis Business Information Solutions B.V.</t>
+  </si>
+  <si>
+    <t>NL_EUR_CCR_PRIMARY</t>
+  </si>
+  <si>
+    <t>3408-999999-135101-XX0000-FR41218800-9999999-3302-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204101-XX0000-FR40113100-9999999-3302-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-135109-XX0000-FR41218800-9999999-3302-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204109-XX0000-FR40113100-9999999-3302-0000-999999</t>
+  </si>
+  <si>
+    <t>3405 - LexisNexis Business Information Solutions Holding SA</t>
+  </si>
+  <si>
+    <t>3408-999999-135101-XX0000-FR41218800-9999999-3405-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204101-XX0000-FR40113100-9999999-3405-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-135109-XX0000-FR41218800-9999999-3405-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204109-XX0000-FR40113100-9999999-3405-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-135101-XX0000-FR41218800-9999999-3406-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204101-XX0000-FR40113100-9999999-3406-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-135109-XX0000-FR41218800-9999999-3406-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204109-XX0000-FR40113100-9999999-3406-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-135101-XX0000-FR41218800-9999999-3511-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204101-XX0000-FR40113100-9999999-3511-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-135109-XX0000-FR41218800-9999999-3511-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204109-XX0000-FR40113100-9999999-3511-0000-999999</t>
+  </si>
+  <si>
+    <t>3702 - RELX Holdings Australia Pty Ltd</t>
   </si>
   <si>
     <t>AU_AUD_CCR_PRIMARY</t>
   </si>
   <si>
-    <t>1117-999999-135101-XX0000-XX99999999-9999999-1701-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-204101-XX0000-XX99999999-9999999-1701-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-135109-XX0000-XX99999999-9999999-1701-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-204109-XX0000-XX99999999-9999999-1701-0000-999999</t>
-  </si>
-  <si>
-    <t>1711 - LNRS Data Services Pte Ltd</t>
+    <t>3408-999999-135101-XX0000-FR41218800-9999999-3702-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204101-XX0000-FR40113100-9999999-3702-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-135109-XX0000-FR41218800-9999999-3702-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204109-XX0000-FR40113100-9999999-3702-0000-999999</t>
+  </si>
+  <si>
+    <t>5206 - RELX (UK) Limited (Corp)</t>
+  </si>
+  <si>
+    <t>3408-999999-135101-XX0000-FR41218800-9999999-5206-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204101-XX0000-FR40113100-9999999-5206-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-135109-XX0000-FR41218800-9999999-5206-0000-999999</t>
+  </si>
+  <si>
+    <t>3408-999999-204109-XX0000-FR40113100-9999999-5206-0000-999999</t>
+  </si>
+  <si>
+    <t>3501 - LexisNexis Verlag ARD ORAC GmbH &amp; Co KG</t>
+  </si>
+  <si>
+    <t>1118 - LexisNexis Risk Solutions FL Inc.</t>
+  </si>
+  <si>
+    <t>AT_EUR_CCR_PRIMARY</t>
+  </si>
+  <si>
+    <t>3501-999999-135101-XX0000-XX99999999-9999999-1118-0000-999999</t>
+  </si>
+  <si>
+    <t>3501-999999-204101-XX0000-XX99999999-9999999-1118-0000-999999</t>
+  </si>
+  <si>
+    <t>3501-999999-135109-XX0000-XX99999999-9999999-1118-0000-999999</t>
+  </si>
+  <si>
+    <t>3501-999999-204109-XX0000-XX99999999-9999999-1118-0000-999999</t>
+  </si>
+  <si>
+    <t>2201 - Elsevier Ltd</t>
+  </si>
+  <si>
+    <t>3501-999999-135101-XX0000-XX99999999-9999999-2201-0000-999999</t>
+  </si>
+  <si>
+    <t>3501-999999-204101-XX0000-XX99999999-9999999-2201-0000-999999</t>
+  </si>
+  <si>
+    <t>3501-999999-135109-XX0000-XX99999999-9999999-2201-0000-999999</t>
+  </si>
+  <si>
+    <t>3501-999999-204109-XX0000-XX99999999-9999999-2201-0000-999999</t>
+  </si>
+  <si>
+    <t>3501-999999-135101-XX0000-XX99999999-9999999-3511-0000-999999</t>
+  </si>
+  <si>
+    <t>3501-999999-204101-XX0000-XX99999999-9999999-3511-0000-999999</t>
+  </si>
+  <si>
+    <t>3501-999999-135109-XX0000-XX99999999-9999999-3511-0000-999999</t>
+  </si>
+  <si>
+    <t>3501-999999-204109-XX0000-XX99999999-9999999-3511-0000-999999</t>
+  </si>
+  <si>
+    <t>3512 - PatentSight GmbH</t>
+  </si>
+  <si>
+    <t>3501-999999-135101-XX0000-XX99999999-9999999-3512-0000-999999</t>
+  </si>
+  <si>
+    <t>3501-999999-204101-XX0000-XX99999999-9999999-3512-0000-999999</t>
+  </si>
+  <si>
+    <t>3501-999999-135109-XX0000-XX99999999-9999999-3512-0000-999999</t>
+  </si>
+  <si>
+    <t>3501-999999-204109-XX0000-XX99999999-9999999-3512-0000-999999</t>
+  </si>
+  <si>
+    <t>3506 - LexisNexis BV</t>
+  </si>
+  <si>
+    <t>2102 - Elsevier Inc.</t>
+  </si>
+  <si>
+    <t>BE_EUR_CCR_PRIMARY</t>
+  </si>
+  <si>
+    <t>3506-999999-135101-XX0000-XX99999999-9999999-2102-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204101-XX0000-XX99999999-9999999-2102-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-135109-XX0000-XX99999999-9999999-2102-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204109-XX0000-XX99999999-9999999-2102-0000-999999</t>
+  </si>
+  <si>
+    <t>2501 - Elsevier A/S</t>
+  </si>
+  <si>
+    <t>DK_DKK_CCR_PRIMARY</t>
+  </si>
+  <si>
+    <t>3506-999999-135101-XX0000-XX99999999-9999999-2501-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204101-XX0000-XX99999999-9999999-2501-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-135109-XX0000-XX99999999-9999999-2501-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204109-XX0000-XX99999999-9999999-2501-0000-999999</t>
+  </si>
+  <si>
+    <t>3108 - Portfolio Media, Inc.</t>
+  </si>
+  <si>
+    <t>3506-999999-135101-XX0000-XX99999999-9999999-3108-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204101-XX0000-XX99999999-9999999-3108-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-135109-XX0000-XX99999999-9999999-3108-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204109-XX0000-XX99999999-9999999-3108-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-135101-XX0000-XX99999999-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204101-XX0000-XX99999999-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-135109-XX0000-XX99999999-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204109-XX0000-XX99999999-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-135101-XX0000-XX99999999-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204101-XX0000-XX99999999-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-135109-XX0000-XX99999999-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204109-XX0000-XX99999999-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-135101-XX0000-XX99999999-9999999-3302-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204101-XX0000-XX99999999-9999999-3302-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-135109-XX0000-XX99999999-9999999-3302-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204109-XX0000-XX99999999-9999999-3302-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-135101-XX0000-XX99999999-9999999-3408-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204101-XX0000-XX99999999-9999999-3408-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-135109-XX0000-XX99999999-9999999-3408-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204109-XX0000-XX99999999-9999999-3408-0000-999999</t>
+  </si>
+  <si>
+    <t>3518 - Henchman BV</t>
+  </si>
+  <si>
+    <t>3506-999999-135101-XX0000-XX99999999-9999999-3518-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204101-XX0000-XX99999999-9999999-3518-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-135109-XX0000-XX99999999-9999999-3518-0000-999999</t>
+  </si>
+  <si>
+    <t>3506-999999-204109-XX0000-XX99999999-9999999-3518-0000-999999</t>
+  </si>
+  <si>
+    <t>3511-999999-135101-XX0000-XX99999999-9999999-3512-0000-999999</t>
+  </si>
+  <si>
+    <t>3511-999999-204101-XX0000-XX99999999-9999999-3512-0000-999999</t>
+  </si>
+  <si>
+    <t>3511-999999-135109-XX0000-XX99999999-9999999-3512-0000-999999</t>
+  </si>
+  <si>
+    <t>3511-999999-204109-XX0000-XX99999999-9999999-3512-0000-999999</t>
+  </si>
+  <si>
+    <t>3109 - Reed Technology and Information Services LLC (LN)</t>
+  </si>
+  <si>
+    <t>3512-999999-135101-XX0000-XX99999999-9999999-3109-0000-999999</t>
+  </si>
+  <si>
+    <t>3512-999999-204101-XX0000-XX99999999-9999999-3109-0000-999999</t>
+  </si>
+  <si>
+    <t>No Data to Display</t>
+  </si>
+  <si>
+    <t>3512-999999-135109-XX0000-XX99999999-9999999-3109-0000-999999</t>
+  </si>
+  <si>
+    <t>3512-999999-204109-XX0000-XX99999999-9999999-3109-0000-999999</t>
+  </si>
+  <si>
+    <t>3512-999999-135101-XX0000-XX99999999-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3512-999999-204101-XX0000-XX99999999-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3512-999999-135109-XX0000-XX99999999-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3512-999999-204109-XX0000-XX99999999-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3512-999999-135101-XX0000-XX99999999-9999999-3501-0000-999999</t>
+  </si>
+  <si>
+    <t>3512-999999-204101-XX0000-XX99999999-9999999-3501-0000-999999</t>
+  </si>
+  <si>
+    <t>3512-999999-135109-XX0000-XX99999999-9999999-3501-0000-999999</t>
+  </si>
+  <si>
+    <t>3512-999999-204109-XX0000-XX99999999-9999999-3501-0000-999999</t>
+  </si>
+  <si>
+    <t>3518-999999-135101-XX0000-XX99999999-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3518-999999-204101-XX0000-XX99999999-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3518-999999-135109-XX0000-XX99999999-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3518-999999-204109-XX0000-XX99999999-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3601 - Reed Elsevier Information Technology (Beijing) Co. Ltd.- HQ</t>
+  </si>
+  <si>
+    <t>2603 - Reed Elsevier Information Technology (Beijing) Co Ltd</t>
+  </si>
+  <si>
+    <t>CN_CNY_CCR_PRIMARY</t>
+  </si>
+  <si>
+    <t>3601-999999-135101-XX0000-CN11220107-9999999-2603-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-204101-XX0000-CN22020103-9999999-2603-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-135109-XX0000-CN11220107-9999999-2603-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-204109-XX0000-CN22020103-9999999-2603-0000-999999</t>
+  </si>
+  <si>
+    <t>2020-01-02T00:00:00.000+00:00</t>
+  </si>
+  <si>
+    <t>3601-999999-135101-XX0000-CN11220107-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-204101-XX0000-CN22020103-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-135109-XX0000-CN11220107-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-204109-XX0000-CN22020103-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3606 - RELX (Greater China) Limited - Hong Kong</t>
+  </si>
+  <si>
+    <t>HK_HKD_CCR_PRIMARY</t>
+  </si>
+  <si>
+    <t>3601-999999-135101-XX0000-CN11220107-9999999-3606-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-204101-XX0000-CN22020103-9999999-3606-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-135109-XX0000-CN11220107-9999999-3606-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-204109-XX0000-CN22020103-9999999-3606-0000-999999</t>
+  </si>
+  <si>
+    <t>3608 - RELX (Greater China) Limited - China</t>
+  </si>
+  <si>
+    <t>HK_CNY_CCR_PRIMARY</t>
+  </si>
+  <si>
+    <t>3601-999999-135101-XX0000-CN11220107-9999999-3608-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-204101-XX0000-CN22020103-9999999-3608-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-135109-XX0000-CN11220107-9999999-3608-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-204109-XX0000-CN22020103-9999999-3608-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-135101-XX0000-CN11220107-9999999-5206-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-204101-XX0000-CN22020103-9999999-5206-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-135109-XX0000-CN11220107-9999999-5206-0000-999999</t>
+  </si>
+  <si>
+    <t>3601-999999-204109-XX0000-CN22020103-9999999-5206-0000-999999</t>
+  </si>
+  <si>
+    <t>3602 - Reed Elsevier Information Technology (Beijing) Co. Ltd. - Shanghai Branch</t>
+  </si>
+  <si>
+    <t>3602-999999-135101-XX0000-CN11220107-9999999-1118-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-204101-XX0000-CN22020103-9999999-1118-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-135109-XX0000-CN11220107-9999999-1118-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-204109-XX0000-CN22020103-9999999-1118-0000-999999</t>
+  </si>
+  <si>
+    <t>2604 - Reed Elsevier Information Technology (Beijing) Co Ltd Shanghai Branch</t>
+  </si>
+  <si>
+    <t>3602-999999-135101-XX0000-CN11220107-9999999-2604-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-204101-XX0000-CN22020103-9999999-2604-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-135109-XX0000-CN11220107-9999999-2604-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-204109-XX0000-CN22020103-9999999-2604-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-135101-XX0000-CN11220107-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-204101-XX0000-CN22020103-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-135109-XX0000-CN11220107-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-204109-XX0000-CN22020103-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-135101-XX0000-CN11220107-9999999-3608-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-204101-XX0000-CN22020103-9999999-3608-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-135109-XX0000-CN11220107-9999999-3608-0000-999999</t>
+  </si>
+  <si>
+    <t>3602-999999-204109-XX0000-CN22020103-9999999-3608-0000-999999</t>
+  </si>
+  <si>
+    <t>3603 - Reed Elsevier Information Technology (Beijing) Co. Ltd. GTO Shanghai</t>
+  </si>
+  <si>
+    <t>3603-999999-135101-XX0000-CN11220107-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-204101-XX0000-CN22020103-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-135109-XX0000-CN11220107-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-204109-XX0000-CN22020103-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-135101-XX0000-CN11220107-9999999-3606-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-204101-XX0000-CN22020103-9999999-3606-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-135109-XX0000-CN11220107-9999999-3606-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-204109-XX0000-CN22020103-9999999-3606-0000-999999</t>
+  </si>
+  <si>
+    <t>3701 - RELX Trading Australia Pty Limited (LexisNexis)</t>
+  </si>
+  <si>
+    <t>3603-999999-135101-XX0000-CN11220107-9999999-3701-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-204101-XX0000-CN22020103-9999999-3701-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-135109-XX0000-CN11220107-9999999-3701-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-204109-XX0000-CN22020103-9999999-3701-0000-999999</t>
+  </si>
+  <si>
+    <t>3710 - LexisNexis NZ Limited</t>
+  </si>
+  <si>
+    <t>NZ_NZD_CCR_PRIMARY</t>
+  </si>
+  <si>
+    <t>3603-999999-135101-XX0000-CN11220107-9999999-3710-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-204101-XX0000-CN22020103-9999999-3710-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-135109-XX0000-CN11220107-9999999-3710-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-204109-XX0000-CN22020103-9999999-3710-0000-999999</t>
+  </si>
+  <si>
+    <t>3746 - RELX Singapore Pte Limited (Lexis Nexis)</t>
   </si>
   <si>
     <t>SG_SGD_CCR_PRIMARY</t>
   </si>
   <si>
-    <t>1117-999999-135101-XX0000-XX99999999-9999999-1711-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-204101-XX0000-XX99999999-9999999-1711-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-135109-XX0000-XX99999999-9999999-1711-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-204109-XX0000-XX99999999-9999999-1711-0000-999999</t>
-  </si>
-  <si>
-    <t>1803 - LexisNexis Servicos de Analise de Risco Ltda</t>
-  </si>
-  <si>
-    <t>BR_BRL_CCR_PRIMARY</t>
-  </si>
-  <si>
-    <t>1117-999999-135101-XX0000-XX99999999-9999999-1803-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-204101-XX0000-XX99999999-9999999-1803-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-135109-XX0000-XX99999999-9999999-1803-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-204109-XX0000-XX99999999-9999999-1803-0000-999999</t>
-  </si>
-  <si>
-    <t>3110 - RELX Inc. (LEXNEX)</t>
-  </si>
-  <si>
-    <t>1117-999999-135101-XX0000-XX99999999-9999999-3110-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-204101-XX0000-XX99999999-9999999-3110-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-135109-XX0000-XX99999999-9999999-3110-0000-999999</t>
-  </si>
-  <si>
-    <t>1117-999999-204109-XX0000-XX99999999-9999999-3110-0000-999999</t>
-  </si>
-  <si>
-    <t>1118 - LexisNexis Risk Solutions FL Inc.</t>
-  </si>
-  <si>
-    <t>1113 - LexisNexis Claims Solutions Inc.</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-1113-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-1113-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-1113-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-1113-0000-999999</t>
-  </si>
-  <si>
-    <t>1115 - LexisNexis Risk Data Management LLC</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-1115-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-1115-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-1115-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-1115-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1204 - LexisNexis Risk Solutions UK Ltd</t>
-  </si>
-  <si>
-    <t>UK_GBP_CCR_PRIMARY</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>2810 - Masson-Doyma Mexico SA</t>
-  </si>
-  <si>
-    <t>MX_MXN_CCR_PRIMARY</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-2810-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-2810-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-2810-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-2810-0000-999999</t>
-  </si>
-  <si>
-    <t>3103 - LexisNexis of Puerto Rico, Inc.</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-3103-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-3103-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-3103-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-3103-0000-999999</t>
-  </si>
-  <si>
-    <t>3105 - Matthew Bender &amp; Company, Inc.</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-3105-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-3105-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-3105-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-3105-0000-999999</t>
-  </si>
-  <si>
-    <t>3106 - MLex US, Inc.</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-3106-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-3106-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-3106-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-3106-0000-999999</t>
-  </si>
-  <si>
-    <t>3108 - Portfolio Media, Inc.</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-3108-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-3108-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-3108-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-3108-0000-999999</t>
-  </si>
-  <si>
-    <t>3109 - Reed Technology and Information Services LLC (LN)</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-3109-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-3109-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-3109-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-3109-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-3110-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-3110-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-3110-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-3110-0000-999999</t>
-  </si>
-  <si>
-    <t>5101 - RELX Inc. (Corp)</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-5101-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-5101-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-5101-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-5101-0000-999999</t>
-  </si>
-  <si>
-    <t>5103 - RELX Inc. - Global Procurement</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-5103-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-5103-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-5103-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-5103-0000-999999</t>
-  </si>
-  <si>
-    <t>5104 - RELX Inc. - Real Estate</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-5104-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-5104-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-5104-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-5104-0000-999999</t>
-  </si>
-  <si>
-    <t>5105 - RELX Inc. - I&amp;O (US Corp)</t>
-  </si>
-  <si>
-    <t>1118-999999-135101-XX0000-XX99999999-9999999-5105-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204101-XX0000-XX99999999-9999999-5105-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-135109-XX0000-XX99999999-9999999-5105-0000-999999</t>
-  </si>
-  <si>
-    <t>1118-999999-204109-XX0000-XX99999999-9999999-5105-0000-999999</t>
-  </si>
-  <si>
-    <t>1201 - LNRS Data Services Ltd</t>
-  </si>
-  <si>
-    <t>1201-999999-135101-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1201-999999-204101-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1201-999999-135109-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1201-999999-204109-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1201-999999-135101-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1201-999999-204101-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1201-999999-135109-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1201-999999-204109-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1205 - Tracesmart Ltd</t>
-  </si>
-  <si>
-    <t>1201-999999-135101-XX0000-XX99999999-9999999-1205-0000-999999</t>
-  </si>
-  <si>
-    <t>1201-999999-204101-XX0000-XX99999999-9999999-1205-0000-999999</t>
-  </si>
-  <si>
-    <t>1201-999999-135109-XX0000-XX99999999-9999999-1205-0000-999999</t>
-  </si>
-  <si>
-    <t>1201-999999-204109-XX0000-XX99999999-9999999-1205-0000-999999</t>
-  </si>
-  <si>
-    <t>5206 - RELX (UK) Limited (Corp)</t>
-  </si>
-  <si>
-    <t>1201-999999-135101-XX0000-XX99999999-9999999-5206-0000-999999</t>
-  </si>
-  <si>
-    <t>1201-999999-204101-XX0000-XX99999999-9999999-5206-0000-999999</t>
-  </si>
-  <si>
-    <t>1201-999999-135109-XX0000-XX99999999-9999999-5206-0000-999999</t>
-  </si>
-  <si>
-    <t>1201-999999-204109-XX0000-XX99999999-9999999-5206-0000-999999</t>
-  </si>
-  <si>
-    <t>1101 - LNRS Data Services Inc.</t>
-  </si>
-  <si>
-    <t>1204-999999-135101-XX0000-XX99999999-9999999-1101-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-204101-XX0000-XX99999999-9999999-1101-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-135109-XX0000-XX99999999-9999999-1101-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-204109-XX0000-XX99999999-9999999-1101-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-135101-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-204101-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-135109-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-204109-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-135101-XX0000-XX99999999-9999999-1118-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-204101-XX0000-XX99999999-9999999-1118-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-135109-XX0000-XX99999999-9999999-1118-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-204109-XX0000-XX99999999-9999999-1118-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-135101-XX0000-XX99999999-9999999-1201-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-204101-XX0000-XX99999999-9999999-1201-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-135109-XX0000-XX99999999-9999999-1201-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-204109-XX0000-XX99999999-9999999-1201-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-135101-XX0000-XX99999999-9999999-1506-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-204101-XX0000-XX99999999-9999999-1506-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-135109-XX0000-XX99999999-9999999-1506-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-204109-XX0000-XX99999999-9999999-1506-0000-999999</t>
-  </si>
-  <si>
-    <t>3204 - RELX (UK) Limited (LN)</t>
-  </si>
-  <si>
-    <t>1204-999999-135101-XX0000-XX99999999-9999999-3204-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-204101-XX0000-XX99999999-9999999-3204-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-135109-XX0000-XX99999999-9999999-3204-0000-999999</t>
-  </si>
-  <si>
-    <t>1204-999999-204109-XX0000-XX99999999-9999999-3204-0000-999999</t>
-  </si>
-  <si>
-    <t>1205-999999-135101-XX0000-XX99999999-9999999-1201-0000-999999</t>
-  </si>
-  <si>
-    <t>1205-999999-204101-XX0000-XX99999999-9999999-1201-0000-999999</t>
-  </si>
-  <si>
-    <t>1205-999999-135109-XX0000-XX99999999-9999999-1201-0000-999999</t>
-  </si>
-  <si>
-    <t>1205-999999-204109-XX0000-XX99999999-9999999-1201-0000-999999</t>
-  </si>
-  <si>
-    <t>1205-999999-135101-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1205-999999-204101-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1205-999999-135109-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1205-999999-204109-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1302 - LNRS Data Services BV</t>
-  </si>
-  <si>
-    <t>NL_EUR_CCR_PRIMARY</t>
-  </si>
-  <si>
-    <t>1302-999999-135101-XX0000-XX99999999-9999999-1118-0000-999999</t>
-  </si>
-  <si>
-    <t>1302-999999-204101-XX0000-XX99999999-9999999-1118-0000-999999</t>
-  </si>
-  <si>
-    <t>1302-999999-135109-XX0000-XX99999999-9999999-1118-0000-999999</t>
-  </si>
-  <si>
-    <t>1302-999999-204109-XX0000-XX99999999-9999999-1118-0000-999999</t>
-  </si>
-  <si>
-    <t>1402 - RELX France Services SAS</t>
-  </si>
-  <si>
-    <t>2402 - Elsevier Masson SAS</t>
-  </si>
-  <si>
-    <t>FR_EUR_CCR_PRIMARY</t>
-  </si>
-  <si>
-    <t>1402-999999-135101-XX0000-FR41218800-9999999-2402-0000-999999</t>
-  </si>
-  <si>
-    <t>1402-999999-204101-XX0000-FR40113100-9999999-2402-0000-999999</t>
-  </si>
-  <si>
-    <t>1402-999999-135109-XX0000-FR41218800-9999999-2402-0000-999999</t>
-  </si>
-  <si>
-    <t>1402-999999-204109-XX0000-FR40113100-9999999-2402-0000-999999</t>
-  </si>
-  <si>
-    <t>3512 - PatentSight GmbH</t>
-  </si>
-  <si>
-    <t>DE_EUR_CCR_PRIMARY</t>
-  </si>
-  <si>
-    <t>1402-999999-135101-XX0000-FR41218800-9999999-3512-0000-999999</t>
-  </si>
-  <si>
-    <t>1402-999999-204101-XX0000-FR40113100-9999999-3512-0000-999999</t>
-  </si>
-  <si>
-    <t>1402-999999-135109-XX0000-FR41218800-9999999-3512-0000-999999</t>
-  </si>
-  <si>
-    <t>1402-999999-204109-XX0000-FR40113100-9999999-3512-0000-999999</t>
-  </si>
-  <si>
-    <t>1402-999999-135101-XX0000-FR41218800-9999999-5206-0000-999999</t>
-  </si>
-  <si>
-    <t>1402-999999-204101-XX0000-FR40113100-9999999-5206-0000-999999</t>
-  </si>
-  <si>
-    <t>1402-999999-135109-XX0000-FR41218800-9999999-5206-0000-999999</t>
-  </si>
-  <si>
-    <t>1402-999999-204109-XX0000-FR40113100-9999999-5206-0000-999999</t>
-  </si>
-  <si>
-    <t>1506-999999-135101-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1506-999999-204101-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1506-999999-135109-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1506-999999-204109-XX0000-XX99999999-9999999-1204-0000-999999</t>
-  </si>
-  <si>
-    <t>1506-999999-135101-XX0000-XX99999999-9999999-3204-0000-999999</t>
-  </si>
-  <si>
-    <t>1506-999999-204101-XX0000-XX99999999-9999999-3204-0000-999999</t>
-  </si>
-  <si>
-    <t>1506-999999-135109-XX0000-XX99999999-9999999-3204-0000-999999</t>
-  </si>
-  <si>
-    <t>1506-999999-204109-XX0000-XX99999999-9999999-3204-0000-999999</t>
-  </si>
-  <si>
-    <t>1106 - ThreatMetrix, Inc.</t>
-  </si>
-  <si>
-    <t>1701-999999-135101-XX0000-XX99999999-9999999-1106-0000-999999</t>
-  </si>
-  <si>
-    <t>1701-999999-204101-XX0000-XX99999999-9999999-1106-0000-999999</t>
-  </si>
-  <si>
-    <t>1701-999999-135109-XX0000-XX99999999-9999999-1106-0000-999999</t>
-  </si>
-  <si>
-    <t>1701-999999-204109-XX0000-XX99999999-9999999-1106-0000-999999</t>
-  </si>
-  <si>
-    <t>1701-999999-135101-XX0000-XX99999999-9999999-1118-0000-999999</t>
-  </si>
-  <si>
-    <t>1701-999999-204101-XX0000-XX99999999-9999999-1118-0000-999999</t>
-  </si>
-  <si>
-    <t>1701-999999-135109-XX0000-XX99999999-9999999-1118-0000-999999</t>
-  </si>
-  <si>
-    <t>1701-999999-204109-XX0000-XX99999999-9999999-1118-0000-999999</t>
-  </si>
-  <si>
-    <t>1711-999999-135101-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1711-999999-204101-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1711-999999-135109-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1711-999999-204109-XX0000-XX99999999-9999999-1117-0000-999999</t>
-  </si>
-  <si>
-    <t>1901 - LexisNexis Israel Ltd</t>
-  </si>
-  <si>
-    <t>2201 - Elsevier Ltd</t>
-  </si>
-  <si>
-    <t>IL_ILS_CCR_PRIMARY</t>
-  </si>
-  <si>
-    <t>1901-999999-135101-XX0000-XX99999999-9999999-2201-0000-999999</t>
-  </si>
-  <si>
-    <t>1901-999999-204101-XX0000-XX99999999-9999999-2201-0000-999999</t>
-  </si>
-  <si>
-    <t>1901-999999-135109-XX0000-XX99999999-9999999-2201-0000-999999</t>
-  </si>
-  <si>
-    <t>1901-999999-204109-XX0000-XX99999999-9999999-2201-0000-999999</t>
-  </si>
-  <si>
-    <t>2101 - Aries Systems Corporation</t>
-  </si>
-  <si>
-    <t>2102 - Elsevier Inc.</t>
-  </si>
-  <si>
-    <t>2101-999999-135101-XX0000-XX99999999-9999999-2102-0000-999999</t>
-  </si>
-  <si>
-    <t>2101-999999-204101-XX0000-XX99999999-9999999-2102-0000-999999</t>
-  </si>
-  <si>
-    <t>2101-999999-135109-XX0000-XX99999999-9999999-2102-0000-999999</t>
-  </si>
-  <si>
-    <t>2101-999999-204109-XX0000-XX99999999-9999999-2102-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-135101-XX0000-XX99999999-9999999-2101-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204101-XX0000-XX99999999-9999999-2101-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-135109-XX0000-XX99999999-9999999-2101-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204109-XX0000-XX99999999-9999999-2101-0000-999999</t>
-  </si>
-  <si>
-    <t>2104 - Knovel Corporation</t>
-  </si>
-  <si>
-    <t>2102-999999-135101-XX0000-XX99999999-9999999-2104-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204101-XX0000-XX99999999-9999999-2104-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-135109-XX0000-XX99999999-9999999-2104-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204109-XX0000-XX99999999-9999999-2104-0000-999999</t>
-  </si>
-  <si>
-    <t>2193 - Elsevier Canada Inc</t>
-  </si>
-  <si>
-    <t>CA_CAD_CCR_PRIMARY</t>
-  </si>
-  <si>
-    <t>2102-999999-135101-XX0000-XX99999999-9999999-2193-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204101-XX0000-XX99999999-9999999-2193-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-135109-XX0000-XX99999999-9999999-2193-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204109-XX0000-XX99999999-9999999-2193-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-135101-XX0000-XX99999999-9999999-2201-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204101-XX0000-XX99999999-9999999-2201-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-135109-XX0000-XX99999999-9999999-2201-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204109-XX0000-XX99999999-9999999-2201-0000-999999</t>
-  </si>
-  <si>
-    <t>2302 - Elsevier BV</t>
-  </si>
-  <si>
-    <t>2102-999999-135101-XX0000-XX99999999-9999999-2302-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204101-XX0000-XX99999999-9999999-2302-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-135109-XX0000-XX99999999-9999999-2302-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204109-XX0000-XX99999999-9999999-2302-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-135101-XX0000-XX99999999-9999999-2402-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204101-XX0000-XX99999999-9999999-2402-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-135109-XX0000-XX99999999-9999999-2402-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204109-XX0000-XX99999999-9999999-2402-0000-999999</t>
-  </si>
-  <si>
-    <t>2501 - Elsevier A/S</t>
-  </si>
-  <si>
-    <t>DK_DKK_CCR_PRIMARY</t>
-  </si>
-  <si>
-    <t>2102-999999-135101-XX0000-XX99999999-9999999-2501-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204101-XX0000-XX99999999-9999999-2501-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-135109-XX0000-XX99999999-9999999-2501-0000-999999</t>
-  </si>
-  <si>
-    <t>2102-999999-204109-XX0000-XX99999999-9999999-2501-0000-999999</t>
-  </si>
-  <si>
-    <t>FROM_LEGAL_ENTITY_NAME</t>
-  </si>
-  <si>
-    <t>TO_LEGAL_ENTITY_NAME</t>
-  </si>
-  <si>
-    <t>FROM_LEDGER_NAME</t>
-  </si>
-  <si>
-    <t>TO_LEDGER_NAME</t>
-  </si>
-  <si>
-    <t>JE_SOURCE_NAME</t>
-  </si>
-  <si>
-    <t>JE_CATEGORY_NAME</t>
-  </si>
-  <si>
-    <t>TRX_TYPE_ID</t>
-  </si>
-  <si>
-    <t>START_DATE</t>
-  </si>
-  <si>
-    <t>END_DATE</t>
-  </si>
-  <si>
-    <t>Receivables Account</t>
-  </si>
-  <si>
-    <t>Payables Account</t>
-  </si>
-  <si>
-    <t>Source File</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Done</t>
+    <t>3603-999999-135101-XX0000-CN11220107-9999999-3746-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-204101-XX0000-CN22020103-9999999-3746-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-135109-XX0000-CN11220107-9999999-3746-0000-999999</t>
+  </si>
+  <si>
+    <t>3603-999999-204109-XX0000-CN22020103-9999999-3746-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135101-XX0000-XX99999999-9999999-1118-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204101-XX0000-XX99999999-9999999-1118-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135109-XX0000-XX99999999-9999999-1118-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204109-XX0000-XX99999999-9999999-1118-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135101-XX0000-XX99999999-9999999-2102-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204101-XX0000-XX99999999-9999999-2102-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135109-XX0000-XX99999999-9999999-2102-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204109-XX0000-XX99999999-9999999-2102-0000-999999</t>
+  </si>
+  <si>
+    <t>2725 - Elsevier (Singapore) Pte Ltd</t>
+  </si>
+  <si>
+    <t>3606-999999-135101-XX0000-XX99999999-9999999-2725-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204101-XX0000-XX99999999-9999999-2725-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135109-XX0000-XX99999999-9999999-2725-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204109-XX0000-XX99999999-9999999-2725-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135101-XX0000-XX99999999-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204101-XX0000-XX99999999-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135109-XX0000-XX99999999-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204109-XX0000-XX99999999-9999999-3110-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135101-XX0000-XX99999999-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204101-XX0000-XX99999999-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135109-XX0000-XX99999999-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204109-XX0000-XX99999999-9999999-3204-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135101-XX0000-XX99999999-9999999-3601-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204101-XX0000-XX99999999-9999999-3601-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135109-XX0000-XX99999999-9999999-3601-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204109-XX0000-XX99999999-9999999-3601-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135101-XX0000-XX99999999-9999999-3608-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204101-XX0000-XX99999999-9999999-3608-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135109-XX0000-XX99999999-9999999-3608-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204109-XX0000-XX99999999-9999999-3608-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135101-XX0000-XX99999999-9999999-3701-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204101-XX0000-XX99999999-9999999-3701-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135109-XX0000-XX99999999-9999999-3701-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204109-XX0000-XX99999999-9999999-3701-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135101-XX0000-XX99999999-9999999-3710-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204101-XX0000-XX99999999-9999999-3710-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135109-XX0000-XX99999999-9999999-3710-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204109-XX0000-XX99999999-9999999-3710-0000-999999</t>
+  </si>
+  <si>
+    <t>3717 - RELX India Private Limited (LN)</t>
+  </si>
+  <si>
+    <t>IN_INR_CCR_PRIMARY</t>
+  </si>
+  <si>
+    <t>3606-999999-135101-XX0000-XX99999999-9999999-3717-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204101-XX0000-XX99999999-9999999-3717-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-135109-XX0000-XX99999999-9999999-3717-0000-999999</t>
+  </si>
+  <si>
+    <t>3606-999999-204109-XX0000-XX99999999-9999999-3717-0000-999999</t>
   </si>
 </sst>
 </file>
@@ -861,7 +867,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -882,6 +888,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -904,11 +916,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1242,3721 +1255,4013 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61023FE0-829F-47EC-A333-E740621D87E9}">
-  <dimension ref="A1:M101"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EA3F84F-CC02-49B2-8300-5BFD1D674C3E}">
+  <dimension ref="A1:Y103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="72.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="70.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="62" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="62.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>258</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>259</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>261</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>262</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>263</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>264</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>265</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>266</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>267</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>268</v>
+        <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="L2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="M2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1">
         <v>46031</v>
       </c>
       <c r="J3" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="M3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" t="s">
-        <v>10</v>
-      </c>
-      <c r="M4" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H5" s="1">
         <v>46031</v>
       </c>
       <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
         <v>18</v>
       </c>
-      <c r="K5" t="s">
+      <c r="I6" t="s">
         <v>19</v>
       </c>
-      <c r="L5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" t="s">
-        <v>7</v>
-      </c>
       <c r="J6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" t="s">
         <v>22</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>23</v>
       </c>
-      <c r="L6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H7" s="1">
         <v>46031</v>
       </c>
       <c r="J7" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G8" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J8" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="K8" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="L8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H9" s="1">
         <v>46031</v>
       </c>
       <c r="J9" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="K9" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="L9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J10" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="K10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="L10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H11" s="1">
         <v>46031</v>
       </c>
       <c r="J11" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K11" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="L11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K12" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="L12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H13" s="1">
         <v>46031</v>
       </c>
       <c r="J13" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="K13" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="L13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
       <c r="C14" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="K14" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="L14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H15" s="1">
         <v>46031</v>
       </c>
       <c r="J15" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="K15" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="L15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J16" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K16" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G17" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H17" s="1">
         <v>46031</v>
       </c>
       <c r="J17" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="K17" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="L17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H18" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J18" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="K18" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="L18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H19" s="1">
         <v>46031</v>
       </c>
       <c r="J19" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="K19" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="L19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J20" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="K20" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="L20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E21" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H21" s="1">
         <v>46031</v>
       </c>
       <c r="J21" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="K21" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="L21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J22" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="K22" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="L22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="D23" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E23" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F23" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H23" s="1">
         <v>46031</v>
       </c>
       <c r="J23" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="K23" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="L23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J24" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="K24" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="L24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F25" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H25" s="1">
         <v>46031</v>
       </c>
       <c r="J25" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="K25" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="L25" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F26" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H26" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J26" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s">
+        <v>89</v>
+      </c>
+      <c r="L26" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>76</v>
       </c>
-      <c r="L26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>37</v>
-      </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F27" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G27" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H27" s="1">
         <v>46031</v>
       </c>
       <c r="J27" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s">
+        <v>91</v>
+      </c>
+      <c r="L27" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" t="s">
         <v>78</v>
       </c>
-      <c r="L27" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" t="s">
-        <v>2</v>
-      </c>
       <c r="D28" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J28" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="L28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E29" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F29" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H29" s="1">
         <v>46031</v>
       </c>
       <c r="J29" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K29" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="L29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D30" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E30" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F30" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="K30" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="L30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H31" s="1">
         <v>46031</v>
       </c>
       <c r="J31" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="K31" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="L31" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="E32" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J32" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="K32" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="E33" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F33" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G33" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H33" s="1">
         <v>46031</v>
       </c>
       <c r="J33" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="K33" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="L33" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C34" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E34" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J34" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="K34" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="L34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C35" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E35" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F35" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H35" s="1">
         <v>46031</v>
       </c>
       <c r="J35" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="K35" t="s">
+        <v>114</v>
+      </c>
+      <c r="L35" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>97</v>
       </c>
-      <c r="L35" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D36" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E36" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F36" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J36" t="s">
+        <v>115</v>
+      </c>
+      <c r="K36" t="s">
+        <v>116</v>
+      </c>
+      <c r="L36" t="s">
+        <v>22</v>
+      </c>
+      <c r="M36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" t="s">
         <v>99</v>
       </c>
-      <c r="K36" t="s">
-        <v>100</v>
-      </c>
-      <c r="L36" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" t="s">
-        <v>2</v>
-      </c>
       <c r="D37" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E37" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H37" s="1">
         <v>46031</v>
       </c>
       <c r="J37" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K37" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="L37" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D38" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E38" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H38" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J38" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="K38" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="L38" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M38" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D39" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E39" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G39" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H39" s="1">
         <v>46031</v>
       </c>
       <c r="J39" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="K39" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="L39" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M39" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D40" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E40" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F40" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J40" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="K40" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="L40" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="D41" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E41" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F41" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H41" s="1">
         <v>46031</v>
       </c>
       <c r="J41" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="K41" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="L41" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B42" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="D42" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J42" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="K42" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="L42" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B43" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="D43" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E43" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F43" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H43" s="1">
         <v>46031</v>
       </c>
       <c r="J43" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="K43" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="L43" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="C44" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="E44" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H44" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J44" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="K44" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="L44" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="C45" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="E45" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H45" s="1">
         <v>46031</v>
       </c>
       <c r="J45" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="K45" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E46" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J46" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="K46" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="L46" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M46" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="C47" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E47" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H47" s="1">
         <v>46031</v>
       </c>
       <c r="J47" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="K47" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="L47" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C48" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D48" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E48" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F48" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J48" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="K48" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="L48" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M48" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="B49" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C49" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D49" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E49" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F49" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H49" s="1">
         <v>46031</v>
       </c>
       <c r="J49" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="K49" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="L49" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="B50" t="s">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="C50" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D50" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E50" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F50" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J50" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="K50" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="L50" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="B51" t="s">
-        <v>132</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D51" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E51" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H51" s="1">
         <v>46031</v>
       </c>
       <c r="J51" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="K51" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="L51" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="B52" t="s">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="C52" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D52" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="E52" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F52" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J52" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="K52" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="L52" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M52" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D53" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="E53" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F53" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H53" s="1">
         <v>46031</v>
       </c>
       <c r="J53" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="K53" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="L53" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="B54" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C54" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="D54" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E54" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F54" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H54" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J54" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="K54" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="L54" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M54" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="B55" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C55" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="D55" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E55" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F55" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H55" s="1">
         <v>46031</v>
       </c>
       <c r="J55" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="K55" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="L55" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="B56" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="C56" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D56" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="E56" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F56" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H56" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J56" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="K56" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="L56" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M56" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="C57" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D57" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="E57" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H57" s="1">
         <v>46031</v>
       </c>
       <c r="J57" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="K57" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="L57" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M57" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="B58" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C58" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D58" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="E58" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F58" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H58" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="I58" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J58" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="K58" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="L58" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M58" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="B59" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C59" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D59" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="E59" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H59" s="1">
         <v>46031</v>
       </c>
       <c r="J59" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="K59" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="L59" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M59" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="B60" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="C60" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D60" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="E60" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F60" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H60" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="I60" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J60" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="K60" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="L60" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>52</v>
+        <v>158</v>
       </c>
       <c r="B61" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="C61" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D61" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="E61" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F61" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H61" s="1">
         <v>46031</v>
       </c>
       <c r="J61" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="K61" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="L61" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M61" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="B62" t="s">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D62" t="s">
-        <v>53</v>
+        <v>177</v>
       </c>
       <c r="E62" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F62" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H62" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="I62" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J62" t="s">
+        <v>178</v>
+      </c>
+      <c r="K62" t="s">
+        <v>179</v>
+      </c>
+      <c r="L62" t="s">
+        <v>22</v>
+      </c>
+      <c r="M62" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>158</v>
       </c>
-      <c r="K62" t="s">
-        <v>159</v>
-      </c>
-      <c r="L62" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>122</v>
-      </c>
       <c r="B63" t="s">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="C63" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D63" t="s">
-        <v>53</v>
+        <v>177</v>
       </c>
       <c r="E63" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F63" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H63" s="1">
         <v>46031</v>
       </c>
       <c r="J63" t="s">
+        <v>180</v>
+      </c>
+      <c r="K63" t="s">
+        <v>181</v>
+      </c>
+      <c r="L63" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" t="s">
         <v>160</v>
       </c>
-      <c r="K63" t="s">
-        <v>161</v>
-      </c>
-      <c r="L63" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>122</v>
-      </c>
-      <c r="B64" t="s">
-        <v>52</v>
-      </c>
-      <c r="C64" t="s">
-        <v>53</v>
-      </c>
       <c r="D64" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E64" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F64" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H64" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J64" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="K64" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="L64" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M64" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="B65" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C65" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D65" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="E65" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F65" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G65" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H65" s="1">
         <v>46031</v>
       </c>
       <c r="J65" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="K65" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="L65" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M65" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B66" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="C66" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D66" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E66" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F66" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G66" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H66" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J66" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="K66" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="L66" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M66" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B67" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="C67" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D67" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E67" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F67" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G67" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H67" s="1">
         <v>46031</v>
       </c>
       <c r="J67" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="K67" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="L67" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M67" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B68" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="C68" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="D68" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F68" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G68" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H68" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J68" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="K68" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="L68" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M68" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B69" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="C69" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="D69" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="E69" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F69" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H69" s="1">
         <v>46031</v>
       </c>
       <c r="J69" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="K69" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="L69" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M69" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B70" t="s">
-        <v>179</v>
+        <v>40</v>
       </c>
       <c r="C70" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="D70" t="s">
-        <v>180</v>
+        <v>41</v>
       </c>
       <c r="E70" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F70" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G70" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H70" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="I70" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J70" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="K70" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="L70" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M70" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B71" t="s">
-        <v>179</v>
+        <v>40</v>
       </c>
       <c r="C71" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="D71" t="s">
-        <v>180</v>
+        <v>41</v>
       </c>
       <c r="E71" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F71" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G71" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H71" s="1">
         <v>46031</v>
       </c>
       <c r="J71" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="K71" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="L71" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M71" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B72" t="s">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="C72" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="D72" t="s">
-        <v>53</v>
+        <v>177</v>
       </c>
       <c r="E72" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F72" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G72" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H72" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="I72" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J72" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="K72" t="s">
+        <v>201</v>
+      </c>
+      <c r="L72" t="s">
+        <v>22</v>
+      </c>
+      <c r="M72" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>186</v>
       </c>
-      <c r="L72" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>172</v>
-      </c>
       <c r="B73" t="s">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="C73" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="D73" t="s">
-        <v>53</v>
+        <v>177</v>
       </c>
       <c r="E73" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F73" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G73" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H73" s="1">
         <v>46031</v>
       </c>
       <c r="J73" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="K73" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="L73" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="M73" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="B74" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C74" t="s">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="D74" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E74" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F74" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G74" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H74" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="I74" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J74" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="K74" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="L74" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="B75" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C75" t="s">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="D75" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E75" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F75" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G75" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H75" s="1">
         <v>46031</v>
       </c>
       <c r="J75" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="K75" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="L75" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="B76" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="D76" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="E76" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F76" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G76" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H76" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="I76" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J76" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="K76" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="L76" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="B77" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="C77" t="s">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="D77" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="E77" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F77" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G77" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H77" s="1">
         <v>46031</v>
       </c>
       <c r="J77" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="K77" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="L77" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>14</v>
+        <v>204</v>
       </c>
       <c r="B78" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C78" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="D78" t="s">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="E78" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G78" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H78" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="I78" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J78" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="K78" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="L78" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>14</v>
+        <v>204</v>
       </c>
       <c r="B79" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C79" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="D79" t="s">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="E79" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F79" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H79" s="1">
         <v>46031</v>
       </c>
       <c r="J79" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="K79" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="L79" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>204</v>
       </c>
       <c r="B80" t="s">
-        <v>37</v>
+        <v>218</v>
       </c>
       <c r="C80" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="D80" t="s">
-        <v>2</v>
+        <v>219</v>
       </c>
       <c r="E80" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F80" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G80" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H80" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="I80" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J80" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="K80" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="L80" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>14</v>
+        <v>204</v>
       </c>
       <c r="B81" t="s">
-        <v>37</v>
+        <v>218</v>
       </c>
       <c r="C81" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="D81" t="s">
-        <v>2</v>
+        <v>219</v>
       </c>
       <c r="E81" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F81" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G81" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H81" s="1">
         <v>46031</v>
       </c>
       <c r="J81" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="K81" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="L81" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="B82" t="s">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="C82" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="D82" t="s">
-        <v>2</v>
+        <v>225</v>
       </c>
       <c r="E82" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F82" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G82" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H82" t="s">
-        <v>6</v>
+        <v>165</v>
       </c>
       <c r="I82" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J82" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="K82" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="L82" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="B83" t="s">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="C83" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="D83" t="s">
-        <v>2</v>
+        <v>225</v>
       </c>
       <c r="E83" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F83" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G83" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H83" s="1">
         <v>46031</v>
       </c>
       <c r="J83" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="K83" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="L83" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="B84" t="s">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="C84" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="D84" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E84" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F84" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H84" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I84" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J84" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="K84" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="L84" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="B85" t="s">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="C85" t="s">
-        <v>212</v>
+        <v>171</v>
       </c>
       <c r="D85" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="E85" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F85" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G85" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H85" s="1">
         <v>46031</v>
       </c>
       <c r="J85" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="K85" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="L85" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="B86" t="s">
-        <v>218</v>
+        <v>98</v>
       </c>
       <c r="C86" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D86" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E86" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F86" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G86" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H86" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I86" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J86" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="K86" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="L86" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="B87" t="s">
-        <v>218</v>
+        <v>98</v>
       </c>
       <c r="C87" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D87" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E87" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F87" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G87" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H87" s="1">
         <v>46031</v>
       </c>
       <c r="J87" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="K87" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="L87" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B88" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="C88" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D88" t="s">
-        <v>2</v>
+        <v>225</v>
       </c>
       <c r="E88" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F88" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G88" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H88" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J88" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="K88" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="L88" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B89" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="C89" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D89" t="s">
-        <v>2</v>
+        <v>225</v>
       </c>
       <c r="E89" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F89" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G89" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H89" s="1">
         <v>46031</v>
       </c>
       <c r="J89" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="K89" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="L89" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B90" t="s">
-        <v>227</v>
+        <v>34</v>
       </c>
       <c r="C90" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D90" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E90" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F90" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G90" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H90" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J90" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="K90" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="L90" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>227</v>
+        <v>34</v>
       </c>
       <c r="C91" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D91" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E91" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F91" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G91" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H91" s="1">
         <v>46031</v>
       </c>
       <c r="J91" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="K91" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="L91" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B92" t="s">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="C92" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D92" t="s">
-        <v>233</v>
+        <v>41</v>
       </c>
       <c r="E92" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F92" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G92" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H92" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J92" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="K92" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="L92" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B93" t="s">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="C93" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D93" t="s">
-        <v>233</v>
+        <v>41</v>
       </c>
       <c r="E93" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F93" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G93" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H93" s="1">
         <v>46031</v>
       </c>
       <c r="J93" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="K93" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="L93" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B94" t="s">
-        <v>211</v>
+        <v>158</v>
       </c>
       <c r="C94" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D94" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="E94" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G94" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H94" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J94" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="K94" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="L94" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B95" t="s">
-        <v>211</v>
+        <v>158</v>
       </c>
       <c r="C95" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D95" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="E95" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F95" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G95" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H95" s="1">
         <v>46031</v>
       </c>
       <c r="J95" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="K95" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="L95" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B96" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
       <c r="C96" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D96" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E96" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F96" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G96" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H96" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J96" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="K96" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="L96" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B97" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
       <c r="C97" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D97" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E97" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F97" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G97" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H97" s="1">
         <v>46031</v>
       </c>
       <c r="J97" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="K97" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="L97" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B98" t="s">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="C98" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D98" t="s">
-        <v>174</v>
+        <v>66</v>
       </c>
       <c r="E98" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F98" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G98" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H98" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J98" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="K98" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="L98" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B99" t="s">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="C99" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D99" t="s">
-        <v>174</v>
+        <v>66</v>
       </c>
       <c r="E99" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F99" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G99" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H99" s="1">
         <v>46031</v>
       </c>
       <c r="J99" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="K99" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="L99" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>170</v>
+      </c>
+      <c r="B100" t="s">
         <v>218</v>
       </c>
-      <c r="B100" t="s">
-        <v>251</v>
-      </c>
       <c r="C100" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D100" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="E100" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F100" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G100" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H100" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J100" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="K100" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="L100" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>170</v>
+      </c>
+      <c r="B101" t="s">
         <v>218</v>
       </c>
-      <c r="B101" t="s">
-        <v>251</v>
-      </c>
       <c r="C101" t="s">
-        <v>2</v>
+        <v>171</v>
       </c>
       <c r="D101" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="E101" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F101" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G101" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H101" s="1">
         <v>46031</v>
       </c>
       <c r="J101" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="K101" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="L101" t="s">
-        <v>13</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>170</v>
+      </c>
+      <c r="B102" t="s">
+        <v>267</v>
+      </c>
+      <c r="C102" t="s">
+        <v>171</v>
+      </c>
+      <c r="D102" t="s">
+        <v>268</v>
+      </c>
+      <c r="E102" t="s">
+        <v>16</v>
+      </c>
+      <c r="F102" t="s">
+        <v>16</v>
+      </c>
+      <c r="G102" t="s">
+        <v>17</v>
+      </c>
+      <c r="H102" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" t="s">
+        <v>19</v>
+      </c>
+      <c r="J102" t="s">
+        <v>269</v>
+      </c>
+      <c r="K102" t="s">
+        <v>270</v>
+      </c>
+      <c r="L102" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>170</v>
+      </c>
+      <c r="B103" t="s">
+        <v>267</v>
+      </c>
+      <c r="C103" t="s">
+        <v>171</v>
+      </c>
+      <c r="D103" t="s">
+        <v>268</v>
+      </c>
+      <c r="E103" t="s">
+        <v>16</v>
+      </c>
+      <c r="F103" t="s">
+        <v>16</v>
+      </c>
+      <c r="G103" t="s">
+        <v>17</v>
+      </c>
+      <c r="H103" s="1">
+        <v>46031</v>
+      </c>
+      <c r="J103" t="s">
+        <v>271</v>
+      </c>
+      <c r="K103" t="s">
+        <v>272</v>
+      </c>
+      <c r="L103" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -5094,7 +5399,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A434817-3C85-492D-9FB2-8D9620EB6B23}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BCE5538-7C0B-4214-9A27-81004C6DA63F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -5110,7 +5415,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A149228-7C00-4B10-B4D3-55DF27B122FB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E05EB1F9-4857-4BE9-9951-0D09F87B62CA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -5118,16 +5423,16 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32EE4B36-670C-4260-8220-73BED1604D88}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B652C5B-D034-4BC1-9FC5-82D303FEC8F4}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Sharedpointrequest/CurrentExcelItem.xlsx
+++ b/Sharedpointrequest/CurrentExcelItem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA Folders\Migration\Fusion_ICRules\Sharedpointrequest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC803D27-FA3C-48D4-87AF-E6432DFE7B9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA4E7313-A363-4BA7-8E97-2E08D09F2E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4245" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{BA92EEC4-E084-4429-A8B5-E13039E2C393}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA92EEC4-E084-4429-A8B5-E13039E2C393}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="275">
   <si>
     <t>FROM_LEGAL_ENTITY_NAME</t>
   </si>
@@ -668,6 +668,9 @@
     <t>3603-999999-204109-XX0000-CN22020103-9999999-3110-0000-999999</t>
   </si>
   <si>
+    <t xml:space="preserve"> You must enter a unique combination of from ledger and legal entity, to ledger and legal entity, and source and category or transaction type. (FUN-720168)</t>
+  </si>
+  <si>
     <t>3603-999999-135101-XX0000-CN11220107-9999999-3606-0000-999999</t>
   </si>
   <si>
@@ -741,6 +744,9 @@
   </si>
   <si>
     <t>3606-999999-204109-XX0000-XX99999999-9999999-1118-0000-999999</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Receivables/Payables Account combination cannot be used; it either does not exist, or using it here is not permitted.</t>
   </si>
   <si>
     <t>3606-999999-135101-XX0000-XX99999999-9999999-2102-0000-999999</t>
@@ -4206,6 +4212,9 @@
       <c r="L74" t="s">
         <v>22</v>
       </c>
+      <c r="M74" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
@@ -4241,6 +4250,9 @@
       <c r="L75" t="s">
         <v>26</v>
       </c>
+      <c r="M75" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
@@ -4271,13 +4283,16 @@
         <v>19</v>
       </c>
       <c r="J76" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L76" t="s">
         <v>22</v>
+      </c>
+      <c r="M76" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
@@ -4306,13 +4321,16 @@
         <v>46031</v>
       </c>
       <c r="J77" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K77" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L77" t="s">
         <v>26</v>
+      </c>
+      <c r="M77" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
@@ -4320,7 +4338,7 @@
         <v>204</v>
       </c>
       <c r="B78" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C78" t="s">
         <v>160</v>
@@ -4344,13 +4362,16 @@
         <v>19</v>
       </c>
       <c r="J78" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K78" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L78" t="s">
         <v>22</v>
+      </c>
+      <c r="M78" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
@@ -4358,7 +4379,7 @@
         <v>204</v>
       </c>
       <c r="B79" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C79" t="s">
         <v>160</v>
@@ -4379,13 +4400,16 @@
         <v>46031</v>
       </c>
       <c r="J79" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K79" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L79" t="s">
         <v>26</v>
+      </c>
+      <c r="M79" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
@@ -4393,13 +4417,13 @@
         <v>204</v>
       </c>
       <c r="B80" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C80" t="s">
         <v>160</v>
       </c>
       <c r="D80" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E80" t="s">
         <v>16</v>
@@ -4417,27 +4441,30 @@
         <v>19</v>
       </c>
       <c r="J80" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K80" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L80" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M80" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>204</v>
       </c>
       <c r="B81" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C81" t="s">
         <v>160</v>
       </c>
       <c r="D81" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E81" t="s">
         <v>16</v>
@@ -4452,27 +4479,30 @@
         <v>46031</v>
       </c>
       <c r="J81" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K81" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L81" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M81" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>204</v>
       </c>
       <c r="B82" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C82" t="s">
         <v>160</v>
       </c>
       <c r="D82" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E82" t="s">
         <v>16</v>
@@ -4490,27 +4520,30 @@
         <v>19</v>
       </c>
       <c r="J82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K82" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L82" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M82" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>204</v>
       </c>
       <c r="B83" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C83" t="s">
         <v>160</v>
       </c>
       <c r="D83" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E83" t="s">
         <v>16</v>
@@ -4525,16 +4558,19 @@
         <v>46031</v>
       </c>
       <c r="J83" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K83" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L83" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M83" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>170</v>
       </c>
@@ -4563,16 +4599,19 @@
         <v>19</v>
       </c>
       <c r="J84" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K84" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L84" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M84" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>170</v>
       </c>
@@ -4598,16 +4637,19 @@
         <v>46031</v>
       </c>
       <c r="J85" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K85" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L85" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M85" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>170</v>
       </c>
@@ -4636,16 +4678,16 @@
         <v>19</v>
       </c>
       <c r="J86" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K86" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L86" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>170</v>
       </c>
@@ -4671,27 +4713,27 @@
         <v>46031</v>
       </c>
       <c r="J87" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K87" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L87" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>170</v>
       </c>
       <c r="B88" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C88" t="s">
         <v>171</v>
       </c>
       <c r="D88" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E88" t="s">
         <v>16</v>
@@ -4709,27 +4751,27 @@
         <v>19</v>
       </c>
       <c r="J88" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K88" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L88" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>170</v>
       </c>
       <c r="B89" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C89" t="s">
         <v>171</v>
       </c>
       <c r="D89" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E89" t="s">
         <v>16</v>
@@ -4744,16 +4786,16 @@
         <v>46031</v>
       </c>
       <c r="J89" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K89" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L89" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>170</v>
       </c>
@@ -4782,16 +4824,16 @@
         <v>19</v>
       </c>
       <c r="J90" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K90" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L90" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>170</v>
       </c>
@@ -4817,16 +4859,16 @@
         <v>46031</v>
       </c>
       <c r="J91" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K91" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L91" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>170</v>
       </c>
@@ -4855,16 +4897,16 @@
         <v>19</v>
       </c>
       <c r="J92" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K92" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L92" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>170</v>
       </c>
@@ -4890,16 +4932,16 @@
         <v>46031</v>
       </c>
       <c r="J93" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K93" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L93" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>170</v>
       </c>
@@ -4928,16 +4970,19 @@
         <v>19</v>
       </c>
       <c r="J94" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K94" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L94" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M94" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>170</v>
       </c>
@@ -4963,16 +5008,19 @@
         <v>46031</v>
       </c>
       <c r="J95" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K95" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L95" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M95" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>170</v>
       </c>
@@ -5001,16 +5049,19 @@
         <v>19</v>
       </c>
       <c r="J96" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K96" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L96" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M96" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>170</v>
       </c>
@@ -5036,21 +5087,24 @@
         <v>46031</v>
       </c>
       <c r="J97" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K97" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L97" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M97" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>170</v>
       </c>
       <c r="B98" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C98" t="s">
         <v>171</v>
@@ -5074,21 +5128,24 @@
         <v>19</v>
       </c>
       <c r="J98" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K98" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L98" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M98" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>170</v>
       </c>
       <c r="B99" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C99" t="s">
         <v>171</v>
@@ -5109,27 +5166,30 @@
         <v>46031</v>
       </c>
       <c r="J99" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K99" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L99" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M99" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>170</v>
       </c>
       <c r="B100" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C100" t="s">
         <v>171</v>
       </c>
       <c r="D100" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E100" t="s">
         <v>16</v>
@@ -5147,27 +5207,30 @@
         <v>19</v>
       </c>
       <c r="J100" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K100" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L100" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M100" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>170</v>
       </c>
       <c r="B101" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C101" t="s">
         <v>171</v>
       </c>
       <c r="D101" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E101" t="s">
         <v>16</v>
@@ -5182,27 +5245,30 @@
         <v>46031</v>
       </c>
       <c r="J101" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K101" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L101" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M101" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>170</v>
       </c>
       <c r="B102" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C102" t="s">
         <v>171</v>
       </c>
       <c r="D102" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E102" t="s">
         <v>16</v>
@@ -5220,27 +5286,30 @@
         <v>19</v>
       </c>
       <c r="J102" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K102" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L102" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M102" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>170</v>
       </c>
       <c r="B103" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C103" t="s">
         <v>171</v>
       </c>
       <c r="D103" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E103" t="s">
         <v>16</v>
@@ -5255,13 +5324,16 @@
         <v>46031</v>
       </c>
       <c r="J103" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K103" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L103" t="s">
         <v>26</v>
+      </c>
+      <c r="M103" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -5270,6 +5342,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Unknown Document Type" ma:contentTypeID="0x010104" ma:contentTypeVersion="0" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="05d83ceaa0bbd2e3bc716e6e66bd857a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b3d69fe45253d5ff147bb69036b756a7">
     <xsd:element name="properties">
@@ -5383,15 +5464,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -5399,6 +5471,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E05EB1F9-4857-4BE9-9951-0D09F87B62CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BCE5538-7C0B-4214-9A27-81004C6DA63F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5414,25 +5494,17 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E05EB1F9-4857-4BE9-9951-0D09F87B62CA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B652C5B-D034-4BC1-9FC5-82D303FEC8F4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
